--- a/stories/arbres/ATOM-REL.MOQ.001-04.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gauthier est à l'école. La classe range les manteaux. Le couloir sent le savon. Blanche fait tomber son gant. César commence à rire. Le rire est court. Gauthier ne rit pas. Il ne faut pas rire. Gauthier ne répète pas. Il ne faut pas répéter. Gauthier dit : ce n'est pas gentil. Il va vers Blanche. Il ramasse le gant. Il le tend. Blanche le remet. La maîtresse s'approche. César dit : pardon. Le soir, maman vient. Gauthier raconte. Maman dit : tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On dit : ce n'est pas gentil. Gauthier serre la main de maman.</t>
+          <t>Gauthier est à l'école. La classe range les manteaux. Le couloir sent le savon. Blanche fait tomber son gant. César commence à rire. Le rire est court. Gauthier ne rit pas. Il ne faut pas rire. Gauthier ne répète pas. Il ne faut pas répéter. Ce n'est pas gentil. Il va vers Blanche. Il ramasse le gant. Il le tend. Blanche le remet. La maîtresse s'approche. Pardon. Le soir, maman vient. Gauthier raconte. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Gauthier serre la main de maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Gauthier est à l'école. La classe range les manteaux. Le couloir sent le savon. Blanche fait tomber son gant. César commence à rire. Le rire est court. Gauthier ne rit pas. Il ne faut pas rire. Gauthier ne répète pas. Il ne faut pas répéter.
+enfant-m|Ce n'est pas gentil. Il va vers Blanche. Il ramasse le gant. Il le tend.
+narrateur|Blanche le remet. La maîtresse s'approche.
+copain|Pardon.
+narrateur|Le soir, maman vient. Gauthier raconte.
+maman|Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter.
+narrateur|Ce n'est pas gentil.
+narrateur|Gauthier serre la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1467,6 +1495,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|César rit. Que fait Gauthier ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1491,7 +1524,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gauthier n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. Maman est là.</t>
+          <t>Gauthier n'a pas ri. Il n'a pas répété. Il Ce n'est pas gentil. Maman est là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1633,6 +1666,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Gauthier n'a pas ri. Il n'a pas répété. Il
+enfant-f|Ce n'est pas gentil. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Gauthier range son cartable. Maman marche à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-04.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Gauthier serre la main de maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1506,7 @@
           <t>narrateur|César rit. Que fait Gauthier ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
 enfant-f|Ce n'est pas gentil. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Gauthier range son cartable. Maman marche à côté.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.001-04.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gauthier ne rit pas</t>
+          <t>Les gants près du radiateur</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Près du radiateur, le gant de Victorina glisse. Raphaël ramasse, tend, dit que ce n'est pas gentil. Papa l'écoute le soir.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Gauthier est à l'école. La classe range les manteaux. Le couloir sent le savon. Blanche fait tomber son gant. César commence à rire. Le rire est court. Gauthier ne rit pas. Il ne faut pas rire. Gauthier ne répète pas. Il ne faut pas répéter. Ce n'est pas gentil. Il va vers Blanche. Il ramasse le gant. Il le tend. Blanche le remet. La maîtresse s'approche. Pardon. Le soir, maman vient. Gauthier raconte. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Gauthier serre la main de maman.</t>
+          <t>Le radiateur de l'entrée fait tic-tic. Les gants mouillés sèchent en rang. Ça sent la laine chaude. Une petite vapeur monte, toute fine. Tes gants sont encore humides, Raphaël. Tu les poses près du radiateur ? Oui, papa. Ils sont un peu froids. Pose-les à plat. Bravo. Je reviens te chercher. D'accord, papa. En ce moment, la classe range les manteaux. Les fermetures éclair chantent. Victorina tient un gant bleu. Le gant glisse. Il tombe près du radiateur. Un camarade commence un petit rire. Le rire est court. Raphaël n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il va vers Victorina. Il ramasse le gant. La laine est tiède, un peu rêche. Il le tend. Merci, Raphaël. Victorina remet le gant. Elle le pose à plat, près du radiateur. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Le soir, papa pousse la porte. Le radiateur fait encore tic-tic. Tu as les joues chaudes, Raphaël. Tu me racontes le gant ? Le gant de Victorina est tombé. J'ai ramassé. J'ai tendu. Ce n'est pas gentil, de rire. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On va vers l'amie. On aide. C'est du bon travail. Tes gants sont secs, maintenant ? Oui, papa. Donne-moi ta main. Raphaël serre la main de papa. La petite vapeur n'est plus là. Il reste le tic-tic doux. On marche ensemble ? Oui, papa. Les gants restent en rang, tout sages. La laine ne fume plus.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,64 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Gauthier est à l'école. La classe range les manteaux. Le couloir sent le savon. Blanche fait tomber son gant. César commence à rire. Le rire est court. Gauthier ne rit pas. Il ne faut pas rire. Gauthier ne répète pas. Il ne faut pas répéter.
-enfant-m|Ce n'est pas gentil. Il va vers Blanche. Il ramasse le gant. Il le tend.
-narrateur|Blanche le remet. La maîtresse s'approche.
-copain|Pardon.
-narrateur|Le soir, maman vient. Gauthier raconte.
-maman|Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter.
-narrateur|Ce n'est pas gentil.
-narrateur|Gauthier serre la main de maman.</t>
+          <t>narrateur|Le radiateur de l'entrée fait tic-tic.
+narrateur|Les gants mouillés sèchent en rang.
+narrateur|Ça sent la laine chaude.
+narrateur|Une petite vapeur monte, toute fine.
+papa|Tes gants sont encore humides, Raphaël.
+papa|Tu les poses près du radiateur ?
+enfant-m|Oui, papa.
+enfant-m|Ils sont un peu froids.
+papa|Pose-les à plat.
+papa|Bravo.
+papa|Je reviens te chercher.
+enfant-m|D'accord, papa.
+narrateur|En ce moment, la classe range les manteaux.
+narrateur|Les fermetures éclair chantent.
+narrateur|Victorina tient un gant bleu.
+narrateur|Le gant glisse.
+narrateur|Il tombe près du radiateur.
+narrateur|Un camarade commence un petit rire.
+narrateur|Le rire est court.
+narrateur|Raphaël n'est pas là pour rire.
+narrateur|Il ne répète pas.
+enfant-m|Ce n'est pas gentil.
+narrateur|Il va vers Victorina.
+narrateur|Il ramasse le gant.
+narrateur|La laine est tiède, un peu rêche.
+narrateur|Il le tend.
+copine|Merci, Raphaël.
+narrateur|Victorina remet le gant.
+narrateur|Elle le pose à plat, près du radiateur.
+narrateur|La maîtresse s'approche.
+maitresse|On aide.
+maitresse|On n'est pas là pour rire.
+maitresse|On n'est pas là pour répéter.
+enfant-m|On aide.
+narrateur|Le soir, papa pousse la porte.
+narrateur|Le radiateur fait encore tic-tic.
+papa|Tu as les joues chaudes, Raphaël.
+papa|Tu me racontes le gant ?
+enfant-m|Le gant de Victorina est tombé.
+enfant-m|J'ai ramassé.
+enfant-m|J'ai tendu.
+enfant-m|Ce n'est pas gentil, de rire.
+papa|Tu as bien fait.
+papa|Il ne faut pas rire.
+papa|Il ne faut pas répéter.
+papa|On va vers l'amie.
+papa|On aide.
+papa|C'est du bon travail.
+papa|Tes gants sont secs, maintenant ?
+enfant-m|Oui, papa.
+papa|Donne-moi ta main.
+narrateur|Raphaël serre la main de papa.
+narrateur|La petite vapeur n'est plus là.
+narrateur|Il reste le tic-tic doux.
+papa|On marche ensemble ?
+enfant-m|Oui, papa.
+narrateur|Les gants restent en rang, tout sages.
+narrateur|La laine ne fume plus.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1347,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>César rit. Que fait Gauthier ?</t>
+          <t>Un camarade rit. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1503,7 +1565,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|César rit. Que fait Gauthier ?</t>
+          <t>narrateur|Un camarade rit.
+narrateur|Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1531,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Gauthier n'a pas ri. Il n'a pas répété. Il Ce n'est pas gentil. Maman est là.</t>
+          <t>Raphaël n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. Il a ramassé le gant. Bravo, Raphaël. C'est du bon travail. On n'est pas là pour rire. On n'est pas là pour répéter. J'ai aidé Victorina. Oui. Tu es allé vers elle.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,8 +1738,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Gauthier n'a pas ri. Il n'a pas répété. Il
-enfant-f|Ce n'est pas gentil. Maman est là.</t>
+          <t>narrateur|Raphaël n'a pas ri.
+narrateur|Il n'a pas répété.
+narrateur|Il a dit : ce n'est pas gentil.
+narrateur|Il a ramassé le gant.
+papa|Bravo, Raphaël.
+papa|C'est du bon travail.
+papa|On n'est pas là pour rire.
+papa|On n'est pas là pour répéter.
+enfant-m|J'ai aidé Victorina.
+papa|Oui.
+papa|Tu es allé vers elle.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Gauthier range son cartable. Maman marche à côté.</t>
+          <t>Raphaël range son cartable. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, papa. Le gant de Victorina sèche à plat. On rentre ? Oui. Papa marche à côté. Le radiateur fait encore tic-tic, derrière la porte.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1912,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Gauthier range son cartable. Maman marche à côté.</t>
+          <t>narrateur|Raphaël range son cartable.
+narrateur|Le zip fait un petit bruit.
+papa|Tu as fini de ranger ?
+enfant-m|Oui, papa.
+papa|Le gant de Victorina sèche à plat.
+papa|On rentre ?
+enfant-m|Oui.
+narrateur|Papa marche à côté.
+narrateur|Le radiateur fait encore tic-tic, derrière la porte.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1948,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai ramassé le gant. Ce n'est pas gentil, de rire. Bravo. Tu as fait du bon travail. Les gants sont secs, en rang. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2088,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai ramassé le gant.
+enfant-m|Ce n'est pas gentil, de rire.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|Les gants sont secs, en rang.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2153,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-04.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le radiateur de l'entrée fait tic-tic. Les gants mouillés sèchent en rang. Ça sent la laine chaude. Une petite vapeur monte, toute fine. Tes gants sont encore humides, Raphaël. Tu les poses près du radiateur ? Oui, papa. Ils sont un peu froids. Pose-les à plat. Bravo. Je reviens te chercher. D'accord, papa. En ce moment, la classe range les manteaux. Les fermetures éclair chantent. Victorina tient un gant bleu. Le gant glisse. Il tombe près du radiateur. Un camarade commence un petit rire. Le rire est court. Raphaël n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il va vers Victorina. Il ramasse le gant. La laine est tiède, un peu rêche. Il le tend. Merci, Raphaël. Victorina remet le gant. Elle le pose à plat, près du radiateur. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Le soir, papa pousse la porte. Le radiateur fait encore tic-tic. Tu as les joues chaudes, Raphaël. Tu me racontes le gant ? Le gant de Victorina est tombé. J'ai ramassé. J'ai tendu. Ce n'est pas gentil, de rire. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On va vers l'amie. On aide. C'est du bon travail. Tes gants sont secs, maintenant ? Oui, papa. Donne-moi ta main. Raphaël serre la main de papa. La petite vapeur n'est plus là. Il reste le tic-tic doux. On marche ensemble ? Oui, papa. Les gants restent en rang, tout sages. La laine ne fume plus.</t>
+          <t>Le radiateur de l'entrée fait tic-tic. Les gants mouillés sèchent en rang. Ça sent la laine chaude. Une petite vapeur monte, toute fine. Tes gants sont encore humides, Raphaël. Tu les poses près du radiateur ? Oui, papa. Ils sont un peu froids. Pose-les à plat. Bravo. Je reviens te chercher. D'accord, papa. En ce moment, la classe range les manteaux. Les fermetures éclair chantent. Victorina tient un gant bleu. Le gant glisse. Il tombe près du radiateur. Un camarade commence un petit rire. Le rire est court. Raphaël n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il va vers Victorina. Il ramasse le gant. La laine est tiède, un peu rêche. Il le tend. Merci, Raphaël. Victorina remet le gant. Elle le pose à plat, près du radiateur. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Le soir, papa pousse la porte. Le radiateur fait encore tic-tic. Tu as les joues chaudes, Raphaël. Tu me racontes le gant ? Le gant de Victorina est tombé. J'ai ramassé. J'ai tendu. Ce n'est pas gentil, de rire. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On va vers l'amie. On aide. Tes gants sont secs, maintenant ? Oui, papa. Donne-moi ta main. Raphaël serre la main de papa. La petite vapeur n'est plus là. Il reste le tic-tic doux. On marche ensemble ? Oui, papa. Les gants restent en rang, tout sages. La laine ne fume plus.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gauthier est à l'école. La classe range les manteaux. Le couloir sent le savon. Blanche fait tomber son gant. César commence à rire. Le rire est court. Gauthier ne rit &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt;. Il ne faut pas rire. Gauthier ne répète pas. Il ne faut pas répéter. Gauthier dit : ce n'est pas gentil. Il va vers Blanche. Il ramasse le gant. Il le tend. Blanche le remet. La maîtresse s'approche. César dit : pardon. Le soir, maman vient. Gauthier raconte. Maman dit : tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On dit : ce n'est pas gentil. Gauthier serre la main de maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le radiateur de l'entrée fait tic-tic. Les gants mouillés sèchent en rang. Ça sent la laine chaude. Une petite vapeur monte, toute fine. Tes gants sont encore humides, Raphaël. Tu les poses près du radiateur ? Oui, papa. Ils sont un peu froids. Pose-les à plat. Bravo. Je reviens te chercher. D'accord, papa. En ce moment, la classe range les manteaux. Les fermetures éclair chantent. Victorina tient un gant bleu. Le gant glisse. Il tombe près du radiateur. Un camarade commence un petit rire. Le rire est court. Raphaël n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il va vers Victorina. Il ramasse le gant. La laine est tiède, un peu rêche. Il le tend. Merci, Raphaël. Victorina remet le gant. Elle le pose à plat, près du radiateur. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Le soir, papa pousse la porte. Le radiateur fait encore tic-tic. Tu as les joues chaudes, Raphaël. Tu me racontes le gant ? Le gant de Victorina est tombé. J'ai ramassé. J'ai tendu. Ce n'est pas gentil, de rire. Tu as bien fait. Il ne faut pas rire. Il ne faut pas répéter. On va vers l'amie. On aide. Tes gants sont secs, maintenant ? Oui, papa. Donne-moi ta main. Raphaël serre la main de papa. La petite vapeur n'est plus là. Il reste le tic-tic doux. On marche ensemble ? Oui, papa. Les gants restent en rang, tout sages. La laine ne fume plus.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1371,7 +1371,6 @@
 papa|Il ne faut pas répéter.
 papa|On va vers l'amie.
 papa|On aide.
-papa|C'est du bon travail.
 papa|Tes gants sont secs, maintenant ?
 enfant-m|Oui, papa.
 papa|Donne-moi ta main.
@@ -1384,7 +1383,6 @@
 narrateur|La laine ne fume plus.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1414,7 +1412,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;César rit. Que fait Gauthier ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade rit. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1569,7 +1567,6 @@
 narrateur|Que fait Raphaël ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1594,12 +1591,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. Il a ramassé le gant. Bravo, Raphaël. C'est du bon travail. On n'est pas là pour rire. On n'est pas là pour répéter. J'ai aidé Victorina. Oui. Tu es allé vers elle.</t>
+          <t>Raphaël n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. Il a ramassé le gant. Bravo, Raphaël. On n'est pas là pour rire. On n'est pas là pour répéter. J'ai aidé Victorina. Oui. Tu es allé vers elle.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gauthier n'a &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt; ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. Il a ramassé le gant. Bravo, Raphaël. On n'est pas là pour rire. On n'est pas là pour répéter. J'ai aidé Victorina. Oui. Tu es allé vers elle.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1743,7 +1740,6 @@
 narrateur|Il a dit : ce n'est pas gentil.
 narrateur|Il a ramassé le gant.
 papa|Bravo, Raphaël.
-papa|C'est du bon travail.
 papa|On n'est pas là pour rire.
 papa|On n'est pas là pour répéter.
 enfant-m|J'ai aidé Victorina.
@@ -1751,7 +1747,6 @@
 papa|Tu es allé vers elle.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1781,7 +1776,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Gauthier range son cartable. Maman marche à côté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël range son cartable. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, papa. Le gant de Victorina sèche à plat. On rentre ? Oui. Papa marche à côté. Le radiateur fait encore tic-tic, derrière la porte.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1923,7 +1918,6 @@
 narrateur|Le radiateur fait encore tic-tic, derrière la porte.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1948,12 +1942,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai ramassé le gant. Ce n'est pas gentil, de rire. Bravo. Tu as fait du bon travail. Les gants sont secs, en rang. L'histoire est finie.</t>
+          <t>J'ai ramassé le gant. Ce n'est pas gentil, de rire. Bravo. Les gants sont secs, en rang.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai ramassé le gant. Ce n'est pas gentil, de rire. Bravo. Les gants sont secs, en rang.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2091,12 +2085,9 @@
           <t>enfant-m|J'ai ramassé le gant.
 enfant-m|Ce n'est pas gentil, de rire.
 papa|Bravo.
-papa|Tu as fait du bon travail.
-narrateur|Les gants sont secs, en rang.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Les gants sont secs, en rang.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2115,7 +2106,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2160,6 +2151,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-04.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-04.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Gauthier, Blanche, César, maman</t>
+          <t>Raphaël, Victorina, papa</t>
         </is>
       </c>
     </row>
